--- a/veterinarian_forms/003_veterinary_anesthesia_consent_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/003_veterinary_anesthesia_consent_form--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'dr_smith'}</t>
+          <t>dr_smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Dr Smith'}</t>
+          <t>Dr Smith</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dr_johnson'}</t>
+          <t>dr_johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dr Johnson'}</t>
+          <t>Dr Johnson</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'owner'}</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Owner'}</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'procedure_1'}</t>
+          <t>procedure_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Procedure 1'}</t>
+          <t>Procedure 1</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'procedure_2'}</t>
+          <t>procedure_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Procedure 2'}</t>
+          <t>Procedure 2</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'note_1'}</t>
+          <t>note_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Note 1'}</t>
+          <t>Note 1</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'note_2'}</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Note 2'}</t>
+          <t>Note 2</t>
         </is>
       </c>
     </row>
